--- a/naver-place-crawler/results_health/성동_PT.xlsx
+++ b/naver-place-crawler/results_health/성동_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>올드짐 상동점</t>
+          <t>에이펙스 이엠에스 스튜디오 부천점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>oldgymsangdong@naver.com</t>
+          <t>apexjon519@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1302-6061</t>
+          <t>0507-1375-7625</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경남 거제시 거제중앙로 1659 2층</t>
+          <t>경기 부천시 원미구 길주로 234 중동힐스테이트상가 2층 2048호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oldgymsangdong</t>
+          <t>https://www.instagram.com/apexems5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w3i7r9h</t>
+          <t>https://talk.naver.com/ct/w41edj</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1116</v>
+        <v>96</v>
       </c>
       <c r="Q2" t="n">
-        <v>53</v>
+        <v>187</v>
       </c>
       <c r="R2" t="n">
-        <v>1169</v>
+        <v>283</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1329786903</t>
+          <t>1021835367</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1329786903</t>
+          <t>https://m.place.naver.com/place/1021835367</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 헬스&amp;PT 수성점</t>
+          <t>스탠다드 피트니스 헬스 PT 부천상동점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>chl3503@naver.com</t>
+          <t>standard_songnae@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1491-7677</t>
+          <t>0507-1402-3452</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구광역시 수성구 청수로26길 36 한성스퀘어 5층</t>
+          <t>경기 부천시 원미구 부일로191번길 26 우신프라자 5층 스탠다드 피트니스 부천상동점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://boddy.imweb.me/</t>
+          <t>https://blog.naver.com/standard_songnae</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ijgb</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>943</v>
+        <v>960</v>
       </c>
       <c r="Q3" t="n">
-        <v>1278</v>
+        <v>1930</v>
       </c>
       <c r="R3" t="n">
-        <v>2221</v>
+        <v>2890</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1885094891</t>
+          <t>1330383759</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885094891</t>
+          <t>https://m.place.naver.com/place/1330383759</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스탠다드 피트니스 헬스 PT 부천상동점</t>
+          <t>빌리프짐 헬스&amp;PT 상동점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>standard_songnae@naver.com</t>
+          <t>beliefgym5@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1402-3452</t>
+          <t>0507-1368-6967</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 부일로191번길 26 우신프라자 5층 스탠다드 피트니스 부천상동점</t>
+          <t>경기 부천시 원미구 길주로 105 8층 빌리프짐 상동점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/standard_songnae</t>
+          <t>https://www.instagram.com/BELIEFGYM_SANGDONG</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,15 +797,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49j5b</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>959</v>
+        <v>1429</v>
       </c>
       <c r="Q4" t="n">
-        <v>1933</v>
+        <v>2298</v>
       </c>
       <c r="R4" t="n">
-        <v>2892</v>
+        <v>3727</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1330383759</t>
+          <t>1793743090</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330383759</t>
+          <t>https://m.place.naver.com/place/1793743090</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -845,34 +853,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>빌리프짐 헬스&amp;PT 상동점</t>
+          <t>메디어트 그룹운동&amp;1:1PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>beliefgym5@naver.com</t>
+          <t>mediet2025@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1368-6967</t>
+          <t>0507-1487-1261</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 길주로 105 8층 빌리프짐 상동점</t>
+          <t>경기 부천시 원미구 길주로 81</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/BELIEFGYM_SANGDONG</t>
+          <t>https://blog.naver.com/mediet2025/224064710210</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -887,15 +895,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/whgdzdh</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1429</v>
+        <v>364</v>
       </c>
       <c r="Q5" t="n">
-        <v>2303</v>
+        <v>256</v>
       </c>
       <c r="R5" t="n">
-        <v>3732</v>
+        <v>620</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1793743090</t>
+          <t>35013539</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1793743090</t>
+          <t>https://m.place.naver.com/place/35013539</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -939,34 +951,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>메디어트 그룹운동&amp;1:1PT</t>
+          <t>디에이트짐 헬스 PT 부천상동2호점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mediet2025@naver.com</t>
+          <t>boyoung2da@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1487-1261</t>
+          <t>0507-1441-2997</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 길주로 81</t>
+          <t>경기 부천시 원미구 상동로 81 801호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mediet2025/224064710210</t>
+          <t>https://blog.naver.com/boyoung2da/224238169312</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -986,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40sp5</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1001,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>364</v>
+        <v>2280</v>
       </c>
       <c r="Q6" t="n">
-        <v>256</v>
+        <v>3534</v>
       </c>
       <c r="R6" t="n">
-        <v>620</v>
+        <v>5814</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>35013539</t>
+          <t>1073116020</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35013539</t>
+          <t>https://m.place.naver.com/place/1073116020</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1033,39 +1049,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>디에이트짐 헬스 PT 부천상동2호점</t>
+          <t>피타짐 부개점 24시헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>boyoung2da@naver.com</t>
+          <t>kimt_company@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1441-2997</t>
+          <t>0507-1331-3618</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 상동로 81 801호</t>
+          <t>경기 부천시 원미구 장말로 1 3층 301, 302, 303, 304호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/boyoung2da/224238169312</t>
+          <t>http://pf.kakao.com/_hIxjIX/chat</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1075,22 +1091,18 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/profile</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1099,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2278</v>
+        <v>13</v>
       </c>
       <c r="Q7" t="n">
-        <v>3528</v>
+        <v>34</v>
       </c>
       <c r="R7" t="n">
-        <v>5806</v>
+        <v>47</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1073116020</t>
+          <t>2060744485</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073116020</t>
+          <t>https://m.place.naver.com/place/2060744485</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1131,39 +1143,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>안녕휘트니스 상동역점 헬스 PT</t>
+          <t>청년피티 상동점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hifitness_sangdong@naver.com</t>
+          <t>cnpt1212@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1388-3495</t>
+          <t>0507-1407-1212</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 상동로 109 상동프라자 611호</t>
+          <t>경기 부천시 원미구 송내대로265번길 17</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hifitness_sangdong</t>
+          <t>https://cnptoffical.qshop.ai/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1173,15 +1185,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4tdfl</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,17 +1205,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>188</v>
+        <v>535</v>
       </c>
       <c r="Q8" t="n">
-        <v>236</v>
+        <v>1473</v>
       </c>
       <c r="R8" t="n">
-        <v>424</v>
+        <v>2008</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1597828278</t>
+          <t>37578803</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1597828278</t>
+          <t>https://m.place.naver.com/place/37578803</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1230,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>브라운크리스탈PT샵</t>
+          <t>안녕휘트니스 상동역점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>browncrystal@naver.com</t>
+          <t>hifitness_sangdong@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1449-8088</t>
+          <t>0507-1388-3495</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 상동로 108 다인타운 9층 901호 브라운크리스탈PT</t>
+          <t>경기 부천시 원미구 상동로 109 상동프라자 611호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/browncrystal</t>
+          <t>https://blog.naver.com/hifitness_sangdong</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1272,10 +1288,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc0a8i</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,17 +1303,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="Q9" t="n">
-        <v>195</v>
+        <v>236</v>
       </c>
       <c r="R9" t="n">
-        <v>385</v>
+        <v>424</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>36395278</t>
+          <t>1597828278</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36395278</t>
+          <t>https://m.place.naver.com/place/1597828278</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1319,39 +1339,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>척추,자세교정</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>청년피티 상동점</t>
+          <t>더플로우 체형교정센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cnpt1212@naver.com</t>
+          <t>theflow2023@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1407-1212</t>
+          <t>0507-1332-4663</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 송내대로265번길 17</t>
+          <t>경기 부천시 원미구 소향로 13 2층 204-2호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cnptoffical.qshop.ai/</t>
+          <t>https://blog.naver.com/theflow2023</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1361,15 +1381,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f90o</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>535</v>
+        <v>157</v>
       </c>
       <c r="Q10" t="n">
-        <v>1494</v>
+        <v>50</v>
       </c>
       <c r="R10" t="n">
-        <v>2029</v>
+        <v>207</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>37578803</t>
+          <t>1695041951</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37578803</t>
+          <t>https://m.place.naver.com/place/1695041951</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1413,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>트래몬트짐 PT</t>
+          <t>바디테크짐 상동점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tremont22@naver.com</t>
+          <t>body_tech_gym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1429-3801</t>
+          <t>0507-1413-5964</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 부일로191번길 30</t>
+          <t>경기 부천시 원미구 도약로 27 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tremontgym</t>
+          <t>https://blog.naver.com/body_tech_gym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1455,18 +1479,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wtnr3mw</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1475,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q11" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="R11" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,15 +1518,113 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1202088204</t>
+          <t>1723548612</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1202088204</t>
+          <t>https://m.place.naver.com/place/1723548612</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>헤일로짐24시 헬스&amp;PT&amp;GX&amp;필라 상동역점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>halogym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1387-9634</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기 부천시 원미구 상동로 87 901호, 903호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/halogym1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5pi0u2</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>2142</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>722</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2864</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1739130426</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1739130426</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/성동_PT.xlsx
+++ b/naver-place-crawler/results_health/성동_PT.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 부천점</t>
+          <t>바디엔지니어스짐 헬스&amp;PT 수성점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>apexjon519@naver.com</t>
+          <t>chl3503@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1375-7625</t>
+          <t>0507-1491-7677</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 234 중동힐스테이트상가 2층 2048호</t>
+          <t>대구 수성구 청수로26길 36 한성스퀘어 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/apexems5</t>
+          <t>https://boddy.imweb.me/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w41edj</t>
+          <t>https://talk.naver.com/ct/wce6a6</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>96</v>
+        <v>945</v>
       </c>
       <c r="Q2" t="n">
-        <v>187</v>
+        <v>1345</v>
       </c>
       <c r="R2" t="n">
-        <v>283</v>
+        <v>2290</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1021835367</t>
+          <t>1885094891</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1021835367</t>
+          <t>https://m.place.naver.com/place/1885094891</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>스탠다드 피트니스 헬스 PT 부천상동점</t>
+          <t>메디어트 그룹운동&amp;1:1PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>standard_songnae@naver.com</t>
+          <t>mediet2025@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1402-3452</t>
+          <t>0507-1487-1261</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부일로191번길 26 우신프라자 5층 스탠다드 피트니스 부천상동점</t>
+          <t>경기 부천시 원미구 길주로 81</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/standard_songnae</t>
+          <t>https://blog.naver.com/mediet2025/224064710210</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ijgb</t>
+          <t>https://talk.naver.com/ct/whgdzdh</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>960</v>
+        <v>365</v>
       </c>
       <c r="Q3" t="n">
-        <v>1930</v>
+        <v>257</v>
       </c>
       <c r="R3" t="n">
-        <v>2890</v>
+        <v>622</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1330383759</t>
+          <t>35013539</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330383759</t>
+          <t>https://m.place.naver.com/place/35013539</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>빌리프짐 헬스&amp;PT 상동점</t>
+          <t>디에이트짐 헬스 PT 부천상동2호점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>beliefgym5@naver.com</t>
+          <t>boyoung2da@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1368-6967</t>
+          <t>0507-1441-2997</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 105 8층 빌리프짐 상동점</t>
+          <t>경기 부천시 원미구 상동로 81 801호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/BELIEFGYM_SANGDONG</t>
+          <t>https://blog.naver.com/boyoung2da/224238169312</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49j5b</t>
+          <t>https://talk.naver.com/ct/w40sp5</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1429</v>
+        <v>2319</v>
       </c>
       <c r="Q4" t="n">
-        <v>2298</v>
+        <v>3624</v>
       </c>
       <c r="R4" t="n">
-        <v>3727</v>
+        <v>5943</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1793743090</t>
+          <t>1073116020</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1793743090</t>
+          <t>https://m.place.naver.com/place/1073116020</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -858,34 +858,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>메디어트 그룹운동&amp;1:1PT</t>
+          <t>피타짐 부개점 24시헬스PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mediet2025@naver.com</t>
+          <t>kimt_company@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1487-1261</t>
+          <t>0507-1331-3618</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 81</t>
+          <t>경기 부천시 원미구 장말로 1 3층 301, 302, 303, 304호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mediet2025/224064710210</t>
+          <t>http://pf.kakao.com/_hIxjIX/chat</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -895,22 +895,18 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/whgdzdh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>364</v>
+        <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>256</v>
+        <v>43</v>
       </c>
       <c r="R5" t="n">
-        <v>620</v>
+        <v>60</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>35013539</t>
+          <t>2060744485</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35013539</t>
+          <t>https://m.place.naver.com/place/2060744485</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -956,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>디에이트짐 헬스 PT 부천상동2호점</t>
+          <t>스탠다드 피트니스 헬스 PT 부천상동점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>boyoung2da@naver.com</t>
+          <t>standard_songnae@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1441-2997</t>
+          <t>0507-1402-3452</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상동로 81 801호</t>
+          <t>경기 부천시 원미구 부일로191번길 26 우신프라자 5층 스탠다드 피트니스 부천상동점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/boyoung2da/224238169312</t>
+          <t>https://blog.naver.com/standard_songnae</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40sp5</t>
+          <t>https://talk.naver.com/ct/w5ijgb</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2280</v>
+        <v>973</v>
       </c>
       <c r="Q6" t="n">
-        <v>3534</v>
+        <v>1938</v>
       </c>
       <c r="R6" t="n">
-        <v>5814</v>
+        <v>2911</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,56 +1028,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1073116020</t>
+          <t>1330383759</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073116020</t>
+          <t>https://m.place.naver.com/place/1330383759</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피타짐 부개점 24시헬스PT</t>
+          <t>빌리프짐 헬스&amp;PT 상동점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kimt_company@naver.com</t>
+          <t>beliefgym5@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1331-3618</t>
+          <t>0507-1368-6967</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 장말로 1 3층 301, 302, 303, 304호</t>
+          <t>경기 부천시 원미구 길주로 105 8층 빌리프짐 상동점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_hIxjIX/chat</t>
+          <t>https://www.instagram.com/BELIEFGYM_SANGDONG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1096,13 +1092,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49j5b</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>13</v>
+        <v>1438</v>
       </c>
       <c r="Q7" t="n">
-        <v>34</v>
+        <v>2248</v>
       </c>
       <c r="R7" t="n">
-        <v>47</v>
+        <v>3686</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2060744485</t>
+          <t>1793743090</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2060744485</t>
+          <t>https://m.place.naver.com/place/1793743090</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1148,34 +1148,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>청년피티 상동점</t>
+          <t>바디채널 짐그라운드 상동점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cnpt1212@naver.com</t>
+          <t>bodych_55@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1407-1212</t>
+          <t>0507-1358-8868</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 송내대로265번길 17</t>
+          <t>경기 부천시 원미구 상동로 83</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cnptoffical.qshop.ai/</t>
+          <t>https://blog.naver.com/bodych_55</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4tdfl</t>
+          <t>https://talk.naver.com/ct/w4s18q</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="Q8" t="n">
-        <v>1473</v>
+        <v>3705</v>
       </c>
       <c r="R8" t="n">
-        <v>2008</v>
+        <v>4254</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,51 +1224,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>37578803</t>
+          <t>36943245</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37578803</t>
+          <t>https://m.place.naver.com/place/36943245</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>척추,자세교정</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>안녕휘트니스 상동역점 헬스 PT</t>
+          <t>더플로우 체형교정센터</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hifitness_sangdong@naver.com</t>
+          <t>theflow2023@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1388-3495</t>
+          <t>0507-1332-4663</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상동로 109 상동프라자 611호</t>
+          <t>경기 부천시 원미구 소향로 13 2층 204-2호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hifitness_sangdong</t>
+          <t>https://blog.naver.com/theflow2023</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc0a8i</t>
+          <t>https://talk.naver.com/ct/w4f90o</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="Q9" t="n">
-        <v>236</v>
+        <v>50</v>
       </c>
       <c r="R9" t="n">
-        <v>424</v>
+        <v>207</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,51 +1322,47 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1597828278</t>
+          <t>1695041951</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1597828278</t>
+          <t>https://m.place.naver.com/place/1695041951</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>척추,자세교정</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더플로우 체형교정센터</t>
+          <t>YS휘트니스 송내점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>theflow2023@naver.com</t>
+          <t>ysfitness2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1332-4663</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 소향로 13 2층 204-2호</t>
+          <t>경기 부천시 원미구 상일로 100 7층 701호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/theflow2023</t>
+          <t>https://blog.naver.com/ysfitness2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1391,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4f90o</t>
+          <t>https://talk.naver.com/ct/w42z53</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,17 +1397,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>157</v>
+        <v>209</v>
       </c>
       <c r="Q10" t="n">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="R10" t="n">
-        <v>207</v>
+        <v>298</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1416,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1695041951</t>
+          <t>2091889709</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695041951</t>
+          <t>https://m.place.naver.com/place/2091889709</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1503,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q11" t="n">
         <v>51</v>
       </c>
       <c r="R11" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1528,7 +1524,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1601,13 +1597,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2142</v>
+        <v>2151</v>
       </c>
       <c r="Q12" t="n">
-        <v>722</v>
+        <v>733</v>
       </c>
       <c r="R12" t="n">
-        <v>2864</v>
+        <v>2884</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1626,7 +1622,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/성동_PT.xlsx
+++ b/naver-place-crawler/results_health/성동_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 헬스&amp;PT 수성점</t>
+          <t>올드짐 상동점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>chl3503@naver.com</t>
+          <t>oldgymsangdong@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1491-7677</t>
+          <t>0507-1302-6061</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구 수성구 청수로26길 36 한성스퀘어 5층</t>
+          <t>경남 거제시 거제중앙로 1659 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://boddy.imweb.me/</t>
+          <t>https://blog.naver.com/oldgymsangdong</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wce6a6</t>
+          <t>https://talk.naver.com/ct/w3i7r9h</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>945</v>
+        <v>1134</v>
       </c>
       <c r="Q2" t="n">
-        <v>1345</v>
+        <v>54</v>
       </c>
       <c r="R2" t="n">
-        <v>2290</v>
+        <v>1188</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1885094891</t>
+          <t>1329786903</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885094891</t>
+          <t>https://m.place.naver.com/place/1329786903</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 81</t>
+          <t>경기도 부천시 원미구 길주로 81</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/whgdzdh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -726,10 +722,10 @@
         <v>365</v>
       </c>
       <c r="Q3" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R3" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -777,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상동로 81 801호</t>
+          <t>경기도 부천시 원미구 상동로 81 801호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40sp5</t>
+          <t>https://talk.naver.com/ct/profile</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2319</v>
+        <v>2334</v>
       </c>
       <c r="Q4" t="n">
-        <v>3624</v>
+        <v>3628</v>
       </c>
       <c r="R4" t="n">
-        <v>5943</v>
+        <v>5962</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -940,7 +936,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -952,29 +948,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스탠다드 피트니스 헬스 PT 부천상동점</t>
+          <t>빌리프짐 헬스&amp;PT 상동점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>standard_songnae@naver.com</t>
+          <t>beliefgym5@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1402-3452</t>
+          <t>0507-1368-6967</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부일로191번길 26 우신프라자 5층 스탠다드 피트니스 부천상동점</t>
+          <t>경기도 부천시 원미구 길주로 105 8층 빌리프짐 상동점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/standard_songnae</t>
+          <t>https://www.instagram.com/BELIEFGYM_SANGDONG</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,19 +985,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ijgb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>973</v>
+        <v>1442</v>
       </c>
       <c r="Q6" t="n">
-        <v>1938</v>
+        <v>2257</v>
       </c>
       <c r="R6" t="n">
-        <v>2911</v>
+        <v>3699</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1020,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1330383759</t>
+          <t>1793743090</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330383759</t>
+          <t>https://m.place.naver.com/place/1793743090</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1042,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>빌리프짐 헬스&amp;PT 상동점</t>
+          <t>헤일로짐24시 헬스&amp;PT&amp;GX&amp;필라 상동역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>beliefgym5@naver.com</t>
+          <t>halogym1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1368-6967</t>
+          <t>0507-1387-9634</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 105 8층 빌리프짐 상동점</t>
+          <t>경기도 부천시 원미구 상동로 87 901호, 903호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/BELIEFGYM_SANGDONG</t>
+          <t>https://blog.naver.com/halogym1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,7 +1079,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,12 +1089,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49j5b</t>
+          <t>https://talk.naver.com/ct/w5pi0u2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1438</v>
+        <v>2155</v>
       </c>
       <c r="Q7" t="n">
-        <v>2248</v>
+        <v>734</v>
       </c>
       <c r="R7" t="n">
-        <v>3686</v>
+        <v>2889</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,51 +1118,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1793743090</t>
+          <t>1739130426</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1793743090</t>
+          <t>https://m.place.naver.com/place/1739130426</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바디채널 짐그라운드 상동점</t>
+          <t>브라운크리스탈PT샵</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bodych_55@naver.com</t>
+          <t>browncrystal@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1358-8868</t>
+          <t>0507-1449-8088</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상동로 83</t>
+          <t>경기 부천시 원미구 상동로 108 다인타운 9층 901호 브라운크리스탈PT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodych_55</t>
+          <t>https://blog.naver.com/browncrystal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1195,7 +1187,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4s18q</t>
+          <t>https://talk.naver.com/ct/wc32u3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>549</v>
+        <v>191</v>
       </c>
       <c r="Q8" t="n">
-        <v>3705</v>
+        <v>195</v>
       </c>
       <c r="R8" t="n">
-        <v>4254</v>
+        <v>386</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1216,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36943245</t>
+          <t>36395278</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36943245</t>
+          <t>https://m.place.naver.com/place/36395278</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1324,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1349,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상일로 100 7층 701호</t>
+          <t>경기도 부천시 원미구 상일로 100 7층 701호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1382,14 +1374,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42z53</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q10" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="R10" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1426,7 +1414,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1524,105 +1512,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>헤일로짐24시 헬스&amp;PT&amp;GX&amp;필라 상동역점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>halogym1@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1387-9634</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기 부천시 원미구 상동로 87 901호, 903호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/halogym1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5pi0u2</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>2151</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>733</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2884</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1739130426</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1739130426</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/성동_PT.xlsx
+++ b/naver-place-crawler/results_health/성동_PT.xlsx
@@ -679,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 길주로 81</t>
+          <t>경기 부천시 원미구 길주로 81</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/whgdzdh</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -773,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 상동로 81 801호</t>
+          <t>경기 부천시 원미구 상동로 81 801호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -803,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/profile</t>
+          <t>https://talk.naver.com/ct/w40sp5</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -965,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 길주로 105 8층 빌리프짐 상동점</t>
+          <t>경기 부천시 원미구 길주로 105 8층 빌리프짐 상동점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -990,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49j5b</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1059,7 +1067,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 상동로 87 901호, 903호</t>
+          <t>경기 부천시 원미구 상동로 87 901호, 903호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1349,7 +1357,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 상일로 100 7층 701호</t>
+          <t>경기 부천시 원미구 상일로 100 7층 701호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1374,10 +1382,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42z53</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1392,10 +1404,10 @@
         <v>211</v>
       </c>
       <c r="Q10" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="R10" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/성동_PT.xlsx
+++ b/naver-place-crawler/results_health/성동_PT.xlsx
@@ -1008,10 +1008,10 @@
         <v>1443</v>
       </c>
       <c r="Q6" t="n">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="R6" t="n">
-        <v>3702</v>
+        <v>3705</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1106,10 +1106,10 @@
         <v>2160</v>
       </c>
       <c r="Q7" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="R7" t="n">
-        <v>2895</v>
+        <v>2896</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>브라운크리스��PT샵</t>
+          <t>브라운크리스탈PT샵</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1157,7 +1157,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상동로 108 다인타운 9층 901호 브라운크리스탈PT</t>
+          <t>경기도 부천시 원미구 상동로 108 다인타운 9층 901호 브라운크리스탈PT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1182,14 +1182,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc32u3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>

--- a/naver-place-crawler/results_health/성동_PT.xlsx
+++ b/naver-place-crawler/results_health/성동_PT.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oldgymsangdong</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="Q2" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="R2" t="n">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mediet2025/224064710210</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,20 +694,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/whgdzdh</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q3" t="n">
         <v>258</v>
       </c>
       <c r="R3" t="n">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -778,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/boyoung2da/224238169312</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,12 +792,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/profile</t>
+          <t>https://talk.naver.com/ct/w40sp5</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -914,10 +918,10 @@
         <v>978</v>
       </c>
       <c r="Q5" t="n">
-        <v>1954</v>
+        <v>1958</v>
       </c>
       <c r="R5" t="n">
-        <v>2932</v>
+        <v>2936</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -948,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>빌리프짐 헬스&amp;PT 상동점</t>
+          <t>헤일로짐24시 헬스&amp;PT&amp;GX&amp;필라 상동역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>beliefgym5@naver.com</t>
+          <t>halogym1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1368-6967</t>
+          <t>0507-1387-9634</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 길주로 105 8층 빌리프짐 상동점</t>
+          <t>경기도 부천시 원미구 상동로 87 901호, 903호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/BELIEFGYM_SANGDONG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -980,7 +984,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -990,13 +994,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5pi0u2</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1005,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1443</v>
+        <v>2160</v>
       </c>
       <c r="Q6" t="n">
-        <v>2262</v>
+        <v>736</v>
       </c>
       <c r="R6" t="n">
-        <v>3705</v>
+        <v>2896</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1793743090</t>
+          <t>1739130426</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1793743090</t>
+          <t>https://m.place.naver.com/place/1739130426</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1042,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헤일로짐24시 헬스&amp;PT&amp;GX&amp;필라 상동역점</t>
+          <t>빌리프짐 헬스&amp;PT 상동점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>halogym1@naver.com</t>
+          <t>beliefgym5@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1387-9634</t>
+          <t>0507-1368-6967</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 상동로 87 901호, 903호</t>
+          <t>경기도 부천시 원미구 길주로 105 8층 빌리프짐 상동점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/halogym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1074,12 +1082,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1089,12 +1097,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5pi0u2</t>
+          <t>https://talk.naver.com/ct/w49j5b</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1103,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2160</v>
+        <v>1443</v>
       </c>
       <c r="Q7" t="n">
-        <v>736</v>
+        <v>2264</v>
       </c>
       <c r="R7" t="n">
-        <v>2896</v>
+        <v>3707</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1739130426</t>
+          <t>1793743090</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1739130426</t>
+          <t>https://m.place.naver.com/place/1793743090</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1135,34 +1143,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>척추,자세교정</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>브라운크리스탈PT샵</t>
+          <t>더플로우 체형교정센터</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>browncrystal@naver.com</t>
+          <t>theflow2023@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1449-8088</t>
+          <t>0507-1332-4663</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 상동로 108 다인타운 9층 901호 브라운크리스탈PT</t>
+          <t>경기 부천시 원미구 소향로 13 2층 204-2호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/browncrystal</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1172,20 +1180,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f90o</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1193,17 +1205,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="Q8" t="n">
-        <v>195</v>
+        <v>50</v>
       </c>
       <c r="R8" t="n">
-        <v>386</v>
+        <v>207</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36395278</t>
+          <t>1695041951</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36395278</t>
+          <t>https://m.place.naver.com/place/1695041951</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1229,34 +1241,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>척추,자세교정</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>더플로우 체형교정센터</t>
+          <t>YS휘트니스 송내점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>theflow2023@naver.com</t>
+          <t>ysfitness2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1332-4663</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 소향로 13 2층 204-2호</t>
+          <t>경기도 부천시 원미구 상일로 100 7층 701호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/theflow2023</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1266,12 +1274,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1281,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4f90o</t>
+          <t>https://talk.naver.com/ct/w42z53</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1291,17 +1299,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>157</v>
+        <v>211</v>
       </c>
       <c r="Q9" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="R9" t="n">
-        <v>207</v>
+        <v>306</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1695041951</t>
+          <t>2091889709</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695041951</t>
+          <t>https://m.place.naver.com/place/2091889709</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1332,25 +1340,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YS휘트니스 송내점</t>
+          <t>스포애니 상동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ysfitness2@naver.com</t>
+          <t>spoany33@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1421-7601</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 상일로 100 7층 701호</t>
+          <t>경기도 부천시 원미구 부일로 293</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ysfitness2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1360,20 +1372,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dzzh</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1385,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>211</v>
+        <v>686</v>
       </c>
       <c r="Q10" t="n">
-        <v>95</v>
+        <v>1670</v>
       </c>
       <c r="R10" t="n">
-        <v>306</v>
+        <v>2356</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1400,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2091889709</t>
+          <t>36314848</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2091889709</t>
+          <t>https://m.place.naver.com/place/36314848</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1422,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>스포애니 상동점</t>
+          <t>다니엘짐 부천상동점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jes393030@naver.com</t>
+          <t>danielgym1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1421-7601</t>
+          <t>0507-1458-9683</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 부일로 293</t>
+          <t>경기도 부천시 원미구 길주로 137</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jes393030</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1454,23 +1470,27 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4bgn0</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1479,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>684</v>
+        <v>1116</v>
       </c>
       <c r="Q11" t="n">
-        <v>1670</v>
+        <v>286</v>
       </c>
       <c r="R11" t="n">
-        <v>2354</v>
+        <v>1402</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1494,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>36314848</t>
+          <t>1967595040</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36314848</t>
+          <t>https://m.place.naver.com/place/1967595040</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/성동_PT.xlsx
+++ b/naver-place-crawler/results_health/성동_PT.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/oldgymsangdong</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="Q2" t="n">
         <v>48</v>
       </c>
       <c r="R2" t="n">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mediet2025/224064710210</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,24 +694,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/whgdzdh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -748,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -782,7 +778,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/boyoung2da/224238169312</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,12 +788,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40sp5</t>
+          <t>https://talk.naver.com/ct/profile</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="Q4" t="n">
         <v>3627</v>
       </c>
       <c r="R4" t="n">
-        <v>5966</v>
+        <v>5967</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -918,10 +914,10 @@
         <v>978</v>
       </c>
       <c r="Q5" t="n">
-        <v>1958</v>
+        <v>1961</v>
       </c>
       <c r="R5" t="n">
-        <v>2936</v>
+        <v>2939</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -940,7 +936,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -974,7 +970,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/halogym1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,12 +980,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1013,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="Q6" t="n">
         <v>736</v>
       </c>
       <c r="R6" t="n">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1038,7 +1034,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1068,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/BELIEFGYM_SANGDONG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,7 +1078,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1092,14 +1088,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49j5b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1136,41 +1128,41 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>척추,자세교정</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>더플로우 체형교정센터</t>
+          <t>스포애니 상동점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>theflow2023@naver.com</t>
+          <t>jes393030@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1332-4663</t>
+          <t>0507-1421-7601</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 소향로 13 2층 204-2호</t>
+          <t>경기도 부천시 원미구 부일로 293</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jes393030</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,24 +1172,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4f90o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,17 +1193,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>157</v>
+        <v>686</v>
       </c>
       <c r="Q8" t="n">
-        <v>50</v>
+        <v>1673</v>
       </c>
       <c r="R8" t="n">
-        <v>207</v>
+        <v>2359</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1212,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1695041951</t>
+          <t>36314848</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695041951</t>
+          <t>https://m.place.naver.com/place/36314848</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1246,25 +1234,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YS휘트니스 송내점</t>
+          <t>다니엘짐 부천상동점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ysfitness2@naver.com</t>
+          <t>danielgym1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1458-9683</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 상일로 100 7층 701호</t>
+          <t>경기 부천시 원미구 길주로 137</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/danielgym1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1274,12 +1266,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,12 +1281,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42z53</t>
+          <t>https://talk.naver.com/ct/w4bgn0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1303,13 +1295,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>211</v>
+        <v>1116</v>
       </c>
       <c r="Q9" t="n">
-        <v>95</v>
+        <v>286</v>
       </c>
       <c r="R9" t="n">
-        <v>306</v>
+        <v>1402</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1310,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2091889709</t>
+          <t>1967595040</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2091889709</t>
+          <t>https://m.place.naver.com/place/1967595040</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1340,29 +1332,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스포애니 상동점</t>
+          <t>1:1 피티 그룹 서킷 트레이닝</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>spoany33@naver.com</t>
+          <t>cnrrneowkd@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1421-7601</t>
+          <t>0507-1419-3235</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 부일로 293</t>
+          <t>경기 부천시 원미구 상일로94번길 13 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/cnrrneowkd</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1372,12 +1364,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,27 +1379,27 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dzzh</t>
+          <t>https://talk.naver.com/ct/w4qf60</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>686</v>
+        <v>127</v>
       </c>
       <c r="Q10" t="n">
-        <v>1670</v>
+        <v>465</v>
       </c>
       <c r="R10" t="n">
-        <v>2356</v>
+        <v>592</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,51 +1408,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>36314848</t>
+          <t>33351603</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36314848</t>
+          <t>https://m.place.naver.com/place/33351603</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>다니엘짐 부천상동점</t>
+          <t>알파플레이스 상동 복싱 &amp; 레슬링</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>danielgym1@naver.com</t>
+          <t>alphaplace@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1458-9683</t>
+          <t>0507-1441-0948</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 길주로 137</t>
+          <t>경기 부천시 원미구 길주로 80 301호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/alpha._.place</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1470,7 +1462,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1485,12 +1477,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4bgn0</t>
+          <t>https://talk.naver.com/ct/w5vhzc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1499,13 +1491,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1116</v>
+        <v>36</v>
       </c>
       <c r="Q11" t="n">
-        <v>286</v>
+        <v>128</v>
       </c>
       <c r="R11" t="n">
-        <v>1402</v>
+        <v>164</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,17 +1506,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1967595040</t>
+          <t>1327142695</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1967595040</t>
+          <t>https://m.place.naver.com/place/1327142695</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/성동_PT.xlsx
+++ b/naver-place-crawler/results_health/성동_PT.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="Q2" t="n">
         <v>48</v>
       </c>
       <c r="R2" t="n">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 길주로 81</t>
+          <t>경기 부천시 원미구 길주로 81</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/whgdzdh</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -773,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 상동로 81 801호</t>
+          <t>경기 부천시 원미구 상동로 81 801호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -803,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/profile</t>
+          <t>https://talk.naver.com/ct/w40sp5</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2340</v>
+        <v>2343</v>
       </c>
       <c r="Q4" t="n">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="R4" t="n">
-        <v>5967</v>
+        <v>5969</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -854,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스탠다드 피트니스 헬스 PT 부천상동점</t>
+          <t>헤일로짐24시 헬스&amp;PT&amp;GX&amp;필라 상동역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>standard_songnae@naver.com</t>
+          <t>halogym1@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1402-3452</t>
+          <t>0507-1387-9634</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 부일로191번길 26 우신프라자 5층 스탠다드 피트니스 부천상동점</t>
+          <t>경기 부천시 원미구 상동로 87 901호, 903호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/standard_songnae</t>
+          <t>https://blog.naver.com/halogym1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -896,13 +900,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5pi0u2</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -911,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>978</v>
+        <v>2160</v>
       </c>
       <c r="Q5" t="n">
-        <v>1961</v>
+        <v>736</v>
       </c>
       <c r="R5" t="n">
-        <v>2939</v>
+        <v>2896</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1330383759</t>
+          <t>1739130426</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330383759</t>
+          <t>https://m.place.naver.com/place/1739130426</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -948,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헤일로짐24시 헬스&amp;PT&amp;GX&amp;필라 상동역점</t>
+          <t>스탠다드 피트니스 헬스 PT 부천상동점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>halogym1@naver.com</t>
+          <t>standard_songnae@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1387-9634</t>
+          <t>0507-1402-3452</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 상동로 87 901호, 903호</t>
+          <t>경기 부천시 원미구 부일로191번길 26 우신프라자 5층 스탠다드 피트니스 부천상동점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/halogym1</t>
+          <t>https://blog.naver.com/standard_songnae</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -995,12 +1003,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5pi0u2</t>
+          <t>https://talk.naver.com/ct/w5ijgb</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1009,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2161</v>
+        <v>978</v>
       </c>
       <c r="Q6" t="n">
-        <v>736</v>
+        <v>1966</v>
       </c>
       <c r="R6" t="n">
-        <v>2897</v>
+        <v>2944</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1739130426</t>
+          <t>1330383759</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1739130426</t>
+          <t>https://m.place.naver.com/place/1330383759</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1041,39 +1049,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>빌리프짐 헬스&amp;PT 상동점</t>
+          <t>피타짐 부개점 24시헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>beliefgym5@naver.com</t>
+          <t>kimt_company@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1368-6967</t>
+          <t>0507-1331-3618</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 길주로 105 8층 빌리프짐 상동점</t>
+          <t>경기 부천시 원미구 장말로 1 3층 301, 302, 303, 304호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/BELIEFGYM_SANGDONG</t>
+          <t>http://pf.kakao.com/_hIxjIX/chat</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1094,7 +1102,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1103,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1443</v>
+        <v>17</v>
       </c>
       <c r="Q7" t="n">
-        <v>2264</v>
+        <v>49</v>
       </c>
       <c r="R7" t="n">
-        <v>3707</v>
+        <v>66</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1793743090</t>
+          <t>2060744485</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1793743090</t>
+          <t>https://m.place.naver.com/place/2060744485</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1140,29 +1148,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>스포애니 상동점</t>
+          <t>YS휘트니스 송내점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jes393030@naver.com</t>
+          <t>ysfitness2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1421-7601</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 부일로 293</t>
+          <t>경기 부천시 원미구 상일로 100 7층 701호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jes393030</t>
+          <t>https://blog.naver.com/ysfitness2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1182,10 +1186,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42z53</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1197,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>686</v>
+        <v>212</v>
       </c>
       <c r="Q8" t="n">
-        <v>1673</v>
+        <v>97</v>
       </c>
       <c r="R8" t="n">
-        <v>2359</v>
+        <v>309</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36314848</t>
+          <t>2091889709</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36314848</t>
+          <t>https://m.place.naver.com/place/2091889709</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1234,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>다니엘짐 부천상동점</t>
+          <t>스포애니 상동점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>danielgym1@naver.com</t>
+          <t>jes393030@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1458-9683</t>
+          <t>0507-1421-7601</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 137</t>
+          <t>경기 부천시 원미구 부일로 293</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/danielgym1</t>
+          <t>https://blog.naver.com/jes393030</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1281,12 +1289,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4bgn0</t>
+          <t>https://talk.naver.com/ct/w4dzzh</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1295,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1116</v>
+        <v>688</v>
       </c>
       <c r="Q9" t="n">
-        <v>286</v>
+        <v>1673</v>
       </c>
       <c r="R9" t="n">
-        <v>1402</v>
+        <v>2361</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1967595040</t>
+          <t>36314848</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1967595040</t>
+          <t>https://m.place.naver.com/place/36314848</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1327,34 +1335,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1:1 피티 그룹 서킷 트레이닝</t>
+          <t>센터오브그래비티 상동본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cnrrneowkd@naver.com</t>
+          <t>tejini123@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1419-3235</t>
+          <t>0507-1426-0826</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상일로94번길 13 3층</t>
+          <t>경기 부천시 원미구 소향로 35 5층 502호 센터오브그래비티</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cnrrneowkd</t>
+          <t>https://blog.naver.com/tejini123</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1379,27 +1387,27 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4qf60</t>
+          <t>https://talk.naver.com/ct/w4cn2p</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>127</v>
+        <v>43</v>
       </c>
       <c r="Q10" t="n">
-        <v>465</v>
+        <v>505</v>
       </c>
       <c r="R10" t="n">
-        <v>592</v>
+        <v>548</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>33351603</t>
+          <t>1135936631</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33351603</t>
+          <t>https://m.place.naver.com/place/1135936631</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1425,34 +1433,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>알파플레이스 상동 복싱 &amp; 레슬링</t>
+          <t>다니엘짐 부천상동점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>alphaplace@naver.com</t>
+          <t>danielgym1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1441-0948</t>
+          <t>0507-1458-9683</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 80 301호</t>
+          <t>경기 부천시 원미구 길주로 137</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/alpha._.place</t>
+          <t>https://blog.naver.com/danielgym1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,7 +1475,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1477,12 +1485,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vhzc</t>
+          <t>https://talk.naver.com/ct/w4bgn0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1491,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>36</v>
+        <v>1116</v>
       </c>
       <c r="Q11" t="n">
-        <v>128</v>
+        <v>286</v>
       </c>
       <c r="R11" t="n">
-        <v>164</v>
+        <v>1402</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1327142695</t>
+          <t>1967595040</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1327142695</t>
+          <t>https://m.place.naver.com/place/1967595040</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/성동_PT.xlsx
+++ b/naver-place-crawler/results_health/성동_PT.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -628,10 +628,10 @@
         <v>1143</v>
       </c>
       <c r="Q2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R2" t="n">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 81</t>
+          <t>경기도 부천시 원미구 길주로 81</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/whgdzdh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -748,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -777,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상동로 81 801호</t>
+          <t>경기도 부천시 원미구 상동로 81 801호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40sp5</t>
+          <t>https://talk.naver.com/ct/profile</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -846,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -875,7 +871,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상동로 87 901호, 903호</t>
+          <t>경기도 부천시 원미구 상동로 87 901호, 903호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -944,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -973,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부일로191번길 26 우신프라자 5층 스탠다드 피트니스 부천상동점</t>
+          <t>경기도 부천시 원미구 부일로191번길 26 우신프라자 5층 스탠다드 피트니스 부천상동점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +994,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ijgb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1042,7 +1034,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1136,37 +1128,41 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YS휘트니스 송내점</t>
+          <t>브라운크리스탈PT샵</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ysfitness2@naver.com</t>
+          <t>browncrystal@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1449-8088</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상일로 100 7층 701호</t>
+          <t>경기 부천시 원미구 상동로 108 다인타운 9층 901호 브라운크리스탈PT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ysfitness2</t>
+          <t>https://blog.naver.com/browncrystal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1191,7 +1187,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42z53</t>
+          <t>https://talk.naver.com/ct/wc32u3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="Q8" t="n">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="R8" t="n">
-        <v>309</v>
+        <v>386</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1216,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2091889709</t>
+          <t>36395278</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2091889709</t>
+          <t>https://m.place.naver.com/place/36395278</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1242,29 +1238,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>스포애니 상동점</t>
+          <t>YS휘트니스 송내점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jes393030@naver.com</t>
+          <t>ysfitness2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1421-7601</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부일로 293</t>
+          <t>경기도 부천시 원미구 상일로 100 7층 701호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jes393030</t>
+          <t>https://blog.naver.com/ysfitness2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1284,14 +1276,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dzzh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,13 +1291,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>688</v>
+        <v>212</v>
       </c>
       <c r="Q9" t="n">
-        <v>1673</v>
+        <v>98</v>
       </c>
       <c r="R9" t="n">
-        <v>2361</v>
+        <v>310</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,51 +1306,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>36314848</t>
+          <t>2091889709</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36314848</t>
+          <t>https://m.place.naver.com/place/2091889709</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>센터오브그래비티 상동본점</t>
+          <t>스포애니 상동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>tejini123@naver.com</t>
+          <t>jes393030@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1426-0826</t>
+          <t>0507-1421-7601</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 소향로 35 5층 502호 센터오브그래비티</t>
+          <t>경기도 부천시 원미구 부일로 293</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tejini123</t>
+          <t>https://blog.naver.com/jes393030</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1382,14 +1370,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4cn2p</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,13 +1385,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>43</v>
+        <v>688</v>
       </c>
       <c r="Q10" t="n">
-        <v>505</v>
+        <v>1671</v>
       </c>
       <c r="R10" t="n">
-        <v>548</v>
+        <v>2359</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1400,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1135936631</t>
+          <t>36314848</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135936631</t>
+          <t>https://m.place.naver.com/place/36314848</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1508,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/성동_PT.xlsx
+++ b/naver-place-crawler/results_health/성동_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>올드짐 상동점</t>
+          <t>와츠핏</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>oldgymsangdong@naver.com</t>
+          <t>whatsfit@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1302-6061</t>
+          <t>02-2233-0974</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경남 거제시 거제중앙로 1659 2층</t>
+          <t>서울특별시 성동구 금호산길 61 3층 301호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oldgymsangdong</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,27 +596,23 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w3i7r9h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1143</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="R2" t="n">
-        <v>1192</v>
+        <v>64</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1329786903</t>
+          <t>1316396572</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1329786903</t>
+          <t>https://m.place.naver.com/place/1316396572</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>메디어트 그룹운동&amp;1:1PT</t>
+          <t>더프라임헬스&amp;PT 신당</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mediet2025@naver.com</t>
+          <t>relieve_gym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1487-1261</t>
+          <t>0507-1379-3638</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 길주로 81</t>
+          <t>서울특별시 성동구 왕십리로 410 i동 101, 102, 103호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mediet2025/224064710210</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,23 +690,27 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mou3</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>365</v>
+        <v>623</v>
       </c>
       <c r="Q3" t="n">
-        <v>258</v>
+        <v>430</v>
       </c>
       <c r="R3" t="n">
-        <v>623</v>
+        <v>1053</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>35013539</t>
+          <t>1318520369</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35013539</t>
+          <t>https://m.place.naver.com/place/1318520369</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -751,39 +751,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>디에이트짐 헬스 PT 부천상동2호점</t>
+          <t>메디앤핏 메디컬트레이닝전문센터 상왕십리점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>boyoung2da@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>medifit2014@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>mediandfit9@gmail.com</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1441-2997</t>
+          <t>0507-1470-4123</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 상동로 81 801호</t>
+          <t>서울특별시 성동구 무학로 18 2,3층 메디앤핏</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/boyoung2da/224238169312</t>
+          <t>http://www.mediandfit.co.kr</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -803,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/profile</t>
+          <t>https://talk.naver.com/ct/wc1hzf</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2343</v>
+        <v>91</v>
       </c>
       <c r="Q4" t="n">
-        <v>3626</v>
+        <v>100</v>
       </c>
       <c r="R4" t="n">
-        <v>5969</v>
+        <v>191</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1073116020</t>
+          <t>1025976659</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073116020</t>
+          <t>https://m.place.naver.com/place/1025976659</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -849,34 +853,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헤일로짐24시 헬스&amp;PT&amp;GX&amp;필라 상동역점</t>
+          <t>서울가설재BT비티아시바PT피티아시바파이프비계임대시공판매</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>halogym1@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1387-9634</t>
+          <t>070-8075-8196</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 상동로 87 901호, 903호</t>
+          <t>서울특별시 성동구 상왕십리동</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/halogym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,42 +890,38 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5pi0u2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2160</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>736</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>2896</v>
+        <v>2</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1739130426</t>
+          <t>1901678362</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1739130426</t>
+          <t>https://m.place.naver.com/place/1901678362</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -947,34 +947,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스탠다드 피트니스 헬스 PT 부천상동점</t>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>standard_songnae@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1402-3452</t>
+          <t>070-8046-5067</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 부일로191번길 26 우신프라자 5층 스탠다드 피트니스 부천상동점</t>
+          <t>서울특별시 성동구 상왕십리동</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/standard_songnae</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,12 +984,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1005,17 +1005,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>978</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1966</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2944</v>
+        <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1330383759</t>
+          <t>1333732152</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330383759</t>
+          <t>https://m.place.naver.com/place/1333732152</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1041,44 +1041,44 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피타짐 부개점 24시헬스PT</t>
+          <t>스포애니 성수역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kimt_company@naver.com</t>
+          <t>spoany_77@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1331-3618</t>
+          <t>0507-1449-9680</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 장말로 1 3층 301, 302, 303, 304호</t>
+          <t>서울특별시 성동구 성수이로20길 3 세종빌딩 B1, B2</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_hIxjIX/chat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1088,13 +1088,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40bll</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1103,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>17</v>
+        <v>1801</v>
       </c>
       <c r="Q7" t="n">
-        <v>49</v>
+        <v>1668</v>
       </c>
       <c r="R7" t="n">
-        <v>66</v>
+        <v>3469</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2060744485</t>
+          <t>1096094842</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2060744485</t>
+          <t>https://m.place.naver.com/place/1096094842</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1135,39 +1139,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>브라운크리스탈PT샵</t>
+          <t>빌드업피트니스 PT 성수역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>browncrystal@naver.com</t>
+          <t>buildupfitness1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1449-8088</t>
+          <t>0507-1313-2799</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상동로 108 다인타운 9층 901호 브라운크리스탈PT</t>
+          <t>서울특별시 성동구 아차산로 97 남영빌딩 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/browncrystal</t>
+          <t>https://www.buildupfitness.co.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1187,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc32u3</t>
+          <t>https://talk.naver.com/ct/w458km</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>191</v>
+        <v>3595</v>
       </c>
       <c r="Q8" t="n">
-        <v>195</v>
+        <v>1039</v>
       </c>
       <c r="R8" t="n">
-        <v>386</v>
+        <v>4634</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36395278</t>
+          <t>1716200143</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36395278</t>
+          <t>https://m.place.naver.com/place/1716200143</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1233,17 +1237,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>요가원</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YS휘트니스 송내점</t>
+          <t>애프터 요가 필라테스 서울숲점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ysfitness2@naver.com</t>
+          <t>ariayj@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1251,12 +1255,12 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 상일로 100 7층 701호</t>
+          <t>서울특별시 성동구 왕십리로 50 지하1층 애프터 요가 서울숲점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ysfitness2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1266,20 +1270,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wobbjv5</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1291,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>212</v>
+        <v>55</v>
       </c>
       <c r="Q9" t="n">
-        <v>98</v>
+        <v>263</v>
       </c>
       <c r="R9" t="n">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,12 +1314,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2091889709</t>
+          <t>1183681566</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2091889709</t>
+          <t>https://m.place.naver.com/place/1183681566</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1323,34 +1331,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스포애니 상동점</t>
+          <t>플렉스 복싱PT 성수본관</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jes393030@naver.com</t>
+          <t>aktkxh7@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1421-7601</t>
+          <t>0507-1490-1421</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구 부일로 293</t>
+          <t>서울특별시 성동구 아차산로7길 4 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jes393030</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1360,12 +1368,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1381,17 +1389,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>688</v>
+        <v>17</v>
       </c>
       <c r="Q10" t="n">
-        <v>1671</v>
+        <v>14</v>
       </c>
       <c r="R10" t="n">
-        <v>2359</v>
+        <v>31</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1400,12 +1408,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>36314848</t>
+          <t>1178941375</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36314848</t>
+          <t>https://m.place.naver.com/place/1178941375</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1417,34 +1425,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>다니엘짐 부천상동점</t>
+          <t>카프킥복싱MMA 성수</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>danielgym1@naver.com</t>
+          <t>onesound_sori@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1458-9683</t>
+          <t>0507-1361-0071</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 137</t>
+          <t>서울특별시 성동구 아차산로7길 3 4층 1호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/danielgym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1454,42 +1462,38 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4bgn0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1116</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>286</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
-        <v>1402</v>
+        <v>16</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1498,15 +1502,8421 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1967595040</t>
+          <t>1218500426</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1967595040</t>
+          <t>https://m.place.naver.com/place/1218500426</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H GYM PT &amp; GT 신금호4호점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>hgym4th@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1348-9408</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 행당로 1 지하1층 03호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dugu</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>433</v>
+      </c>
+      <c r="R12" t="n">
+        <v>530</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1743754433</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1743754433</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>바른피티</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>barunptpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1478-9961</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 한림말5길 9 5층 바른피티</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h4g9</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>329</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>145</v>
+      </c>
+      <c r="R13" t="n">
+        <v>474</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1877534839</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1877534839</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>미용</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>수안스킨</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>sunburst7617@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1312-7617</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 410 아이동 143호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2057713318</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2057713318</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>투엑스휘트니스 센트라스점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2x_centlas@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1421-9811</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 410 센트라스 L동 314호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>1729</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>504</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2233</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>73553317</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/73553317</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>리커버 필라테스 &amp; PT 왕십리</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>kapjun91@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1358-4499</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 고산자로 284 성동샤르망 오피스텔 206호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/recover.pilates.pt</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4wu8b</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>164</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>330</v>
+      </c>
+      <c r="R16" t="n">
+        <v>494</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1740587644</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1740587644</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>하이퍼짐</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8291xc@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1340-8319</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무학봉28길 6 2층</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wqez</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>139</v>
+      </c>
+      <c r="R17" t="n">
+        <v>210</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1252044117</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1252044117</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>바디코드 필라테스&amp;PT 왕십리점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>rnjswl9649@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1484-2237</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 348 4층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a77p</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>389</v>
+      </c>
+      <c r="R18" t="n">
+        <v>708</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1117566859</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1117566859</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>더바른몸PT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>thebarunmom_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1388-7893</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 320 W 에비뉴타워 503호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>107</v>
+      </c>
+      <c r="R19" t="n">
+        <v>158</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1160853922</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1160853922</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>성수PT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>seongsupt@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>support@wetrain.co.kr</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1340-1760</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 연무장7길 12 세대빌딩 305호</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.woondoc.com/coach/9958/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46inv</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>234</v>
+      </c>
+      <c r="R20" t="n">
+        <v>416</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1389448556</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1389448556</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>바디텍쳐 왕십리 청계점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>body_tecture@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1388-8620</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 청계천로 452 1층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://bodytecture.fit/wangsimni</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>198</v>
+      </c>
+      <c r="R21" t="n">
+        <v>379</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1916023185</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1916023185</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>복싱,권투장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>복싱스타디움</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>boxingstadium@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>070-4125-8337</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 아차산로7길 21 지하1층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>19</v>
+      </c>
+      <c r="R22" t="n">
+        <v>29</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1282686844</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1282686844</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>근력학교 한양대점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>strength_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>02-2295-3455</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 마조로 9 4층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yc1y</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>43</v>
+      </c>
+      <c r="R23" t="n">
+        <v>66</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1858628810</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1858628810</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PT 스튜디오 리온 왕십리점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2021reon@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1374-0089</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 고산자로 255 케이타워 7층 PT스튜디오리온 왕십리점</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43wty</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>305</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>257</v>
+      </c>
+      <c r="R24" t="n">
+        <v>562</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1186665953</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1186665953</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>짐아서 피트니스</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>rh6868@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1301-6478</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 성수일로 39 경동빌딩 B1</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xe14</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>364</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>183</v>
+      </c>
+      <c r="R25" t="n">
+        <v>547</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1530150594</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1530150594</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kims psPT Story</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>wpdldoszjavjsl@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1899-0012</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 410 센트라스 상가 i동 103호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1661489663</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1661489663</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>더블와이짐 헬스 &amp; PT 신금호점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>doubleygym3@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1472-8302</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 금호산길 67 지하1층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/doubleygym3</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>1233</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>38</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1271</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1698621612</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1698621612</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>브라보PT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>myengryel@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1321-9882</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 339-1 3층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc9npr</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>877</v>
+      </c>
+      <c r="R28" t="n">
+        <v>933</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>34480326</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34480326</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>휴펫필라테스 &amp; PT 왕십리점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>hu_pet@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 327 3층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>http://www.hupetpilates.com</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4k34l</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>517</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>74</v>
+      </c>
+      <c r="R29" t="n">
+        <v>591</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1792607992</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1792607992</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>아이엠바디 재활PT 옥수점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>dreambody_academy@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1414-9496</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로 173 극동그린아파트상가 1층 107호 아이엠바디</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41rfo</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>201</v>
+      </c>
+      <c r="R30" t="n">
+        <v>229</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1424667601</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1424667601</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>엘리시움코리아 상왕십리점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>elysiumkorea@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1436-0876</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무학로 2 1층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://elysiumkorea.com</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w6ydk11</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>35</v>
+      </c>
+      <c r="R31" t="n">
+        <v>78</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2049347432</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2049347432</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>범핏피트니스 답십리점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>bumfit_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1358-7197</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 천호대로 296 5층, 6층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9d46g8</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>654</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>180</v>
+      </c>
+      <c r="R32" t="n">
+        <v>834</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1788667899</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1788667899</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>나의근육사용설명서 성수본점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>nodajiclub@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1368-3797</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 성수일로10길 26 하우스디세종타워 204호</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43k51</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>82</v>
+      </c>
+      <c r="R33" t="n">
+        <v>117</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>19546029</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19546029</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>좋은습관 PT STUDIO 왕십리</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ghpt_wsr@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1325-1531</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 367 2층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>746</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>31</v>
+      </c>
+      <c r="R34" t="n">
+        <v>777</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1035785053</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1035785053</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PT 모스트짐 성수점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>mostgym2022@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1369-9682</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 상원길 64 2층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mostgym2022</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>235</v>
+      </c>
+      <c r="R35" t="n">
+        <v>269</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1249001855</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1249001855</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>좋은습관PT &amp; GH피트니스 성수</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>goodhabit_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1463-1535</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 아차산로 18 2층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://zrr.kr/r1nDuO</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>166</v>
+      </c>
+      <c r="R36" t="n">
+        <v>257</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1172026047</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1172026047</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>스튜디오에이 필라테스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>studioa_pilates_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>02-2291-3015</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 행당로 84 지하1층 109호 스튜디오에이행당점</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>633</v>
+      </c>
+      <c r="R37" t="n">
+        <v>760</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1233540089</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1233540089</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>바나나짐 헬스 &amp; PT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>bananagym_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1425-1592</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 행당로 35 1층 바나나짐</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dp2a</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>299</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1496</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1795</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1317587781</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1317587781</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>데일리피트니스 PT 성수점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>9_zero2@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1383-0119</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 뚝섬로 400 뚝섬쇼핑센타 3층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3rqb3k</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>397</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>778</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1175</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>18788499</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/18788499</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>인피니티퍼스널트레이닝 PT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>infinity_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1326-2320</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 행당로 6 302호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tgz7</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>38</v>
+      </c>
+      <c r="R40" t="n">
+        <v>71</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>37233073</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37233073</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>해빗피트니스 상왕십리점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>habitfitness_1@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1460-0929</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 386 삼협빌딩 지하 1,2층</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40of0</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>912</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>333</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1245</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1481997682</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1481997682</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>파크짐 왕십리점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>parkgym2019@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>02-2281-1872</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 309 B1층, B2층</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4g054</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1127</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1082</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2209</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>36112469</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36112469</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>셀바디PT 왕십리점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>cellbody_@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1355-4186</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 332 지하1층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>336</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1357</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1693</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1236569384</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1236569384</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>커브스 행당클럽</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>curves278mia@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1399-3071</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 행당로 87 대림리빙프라자 5층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>380</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>95</v>
+      </c>
+      <c r="R44" t="n">
+        <v>475</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>13327944</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13327944</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>김대현피티스튜디오 서울숲성수점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>fxbhirs@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1446-2257</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 상원길 26 b2층</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wf4q28c</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>36</v>
+      </c>
+      <c r="R45" t="n">
+        <v>42</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1090498887</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1090498887</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>큐스페셜PT</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>body_design@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>02-463-3328</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 아차산로 91 2층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/body_design</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>268</v>
+      </c>
+      <c r="R46" t="n">
+        <v>376</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1229063340</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1229063340</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>셧업앤스퀏</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>sas0716@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1371-5347</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로 202 달07애비뉴 지하 1층 B103호 (스타벅스건물)</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gvvu</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>164</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>288</v>
+      </c>
+      <c r="R47" t="n">
+        <v>452</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1075862761</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1075862761</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>모티브짐PT 왕십리점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>moti9498@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1313-2703</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 348 가나빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wuuhluj</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>156</v>
+      </c>
+      <c r="R48" t="n">
+        <v>226</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2078487407</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2078487407</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>찬스짐 PT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>chansgympt@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1379-6480</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 363 401호</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t1bb</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>402</v>
+      </c>
+      <c r="R49" t="n">
+        <v>506</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1472992434</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1472992434</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>동핏 PT STUDIO 신금호점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>dongfit_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1317-4623</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 금호로 151 3층 동핏</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dongfit_pt</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>14</v>
+      </c>
+      <c r="R50" t="n">
+        <v>87</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1936114777</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1936114777</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>가설재비티아시바피티아시바파이프유로폼임대대여설치</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>rodtmdu12@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>070-8084-5055</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 상왕십리동</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1140377824</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1140377824</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>쿼드짐 응봉</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>quadgym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1383-0788</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로 434 대림종합상가 302호, 303호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4124r</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>20</v>
+      </c>
+      <c r="R52" t="n">
+        <v>69</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>33703393</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33703393</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>무브먼트 프로젝트</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>writej@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1311-3426</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 성수일로 1 2층 2호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wchruf</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>618</v>
+      </c>
+      <c r="R53" t="n">
+        <v>692</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1470718226</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1470718226</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>짐타운 포레스트</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>tarzan_gymtown@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1336-8961</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 성수일로1길 1 B1 ,짐타운 포레스트</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ds6b</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>46</v>
+      </c>
+      <c r="R54" t="n">
+        <v>131</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1918723055</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1918723055</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>하웰 재활PT&amp;심리운동</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>hawell_@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>haruwellness604@gmail.com</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1382-4642</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 동호로 102 금호두산아파트 상가 605호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://haruwellness604.wixsite.com/hawell/our-teachers</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4</v>
+      </c>
+      <c r="R55" t="n">
+        <v>4</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2099642259</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2099642259</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>스트레치뱅 옥수점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>stretchbangoksu@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1347-1091</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로 194-1 지상3층 201호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>670</v>
+      </c>
+      <c r="R56" t="n">
+        <v>771</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1537975672</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1537975672</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>포시즌휘트니스 왕십리점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>fseason1636@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1355-1636</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리광장로 17 6층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4at97</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>745</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>850</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1595</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>37638105</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37638105</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>좋은습관 PT STUDIO 옥수</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>goodhabit_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1384-1569</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 매봉길 50 옥수파크힐스상가 B101호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wvlxgom</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>39</v>
+      </c>
+      <c r="R58" t="n">
+        <v>186</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1926574926</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1926574926</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>휘트니스피플 우먼 왕십리역점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1432-3912</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 327 3층</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wea8kxc</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>949</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1044</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1993</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2008913727</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2008913727</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>바디101 헬스PT 성수점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>body101_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1443-8935</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 상원6나길 30 지하2층 B201호</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yxpa</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>545</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>450</v>
+      </c>
+      <c r="R60" t="n">
+        <v>995</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1159422922</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1159422922</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>빅브로짐 성수점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>bigbrogym4@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1351-2848</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 115 엘에스타워 지하1층</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://bigbrogym.com</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w487v2</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>4293</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>2911</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7204</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1400389920</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1400389920</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>후츠피티 왕십리점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>diethaxxi@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1485-2041</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 340 지하2층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ybsm</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>951</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1086</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1073977077</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1073977077</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>테라피티 뚝섬역점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>theraptforyou@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1331-2200</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 상원길 52 지하1층 테라피티</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>129</v>
+      </c>
+      <c r="R63" t="n">
+        <v>231</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1578353949</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1578353949</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>윈썸 pt짐 상왕십리점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>winsome_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1343-9625</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 청계천로 422 지하1층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4xzp5</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>185</v>
+      </c>
+      <c r="R64" t="n">
+        <v>255</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1111213530</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1111213530</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>디짐</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ldk09222@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1444-9016</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 상원길 46 지하1층</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>13</v>
+      </c>
+      <c r="R65" t="n">
+        <v>57</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>521181053</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/521181053</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>플레먼트 짐 PT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>this_ju@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1466-4011</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 마조로1길 6 B1층(행당동, 스페이스예인)</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cjn9</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>490</v>
+      </c>
+      <c r="R66" t="n">
+        <v>631</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1708487213</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1708487213</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>리피티 여성전용 PT 왕십리점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>thebestsuper@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 347 2층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46gm9</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>455</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>372</v>
+      </c>
+      <c r="R67" t="n">
+        <v>827</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1792787026</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1792787026</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>리얼무브먼트 메디컬 트레이닝 센터 PT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>real-movement86@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1424-1377</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 성수일로8길 39 3층 리얼무브먼트</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://realmovement.imweb.me/</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc56be</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>210</v>
+      </c>
+      <c r="R68" t="n">
+        <v>396</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1391605324</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1391605324</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>오아시스GYM 1호점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>barunbodypt@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1405-7323</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 장터길 49 3층 오아시스GYM</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://oasis-gym.up.railway.app/landing</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wlnjaeo</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>430</v>
+      </c>
+      <c r="R69" t="n">
+        <v>562</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>823249514</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/823249514</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>리커버리PT</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>dhehdgus1128@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1379-4435</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 마장로 284 . B1층</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ybqj</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>124</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>40</v>
+      </c>
+      <c r="R70" t="n">
+        <v>164</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1463779102</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1463779102</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>퍼먼츠 체형교정&amp;재활PT</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>pt_jinjungsung@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1316-0430</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 94-1 3층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zt98</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>106</v>
+      </c>
+      <c r="R71" t="n">
+        <v>114</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1909508142</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1909508142</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>키스짐 헬스PT 신금호역점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>kissfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1351-4788</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무수막길 97 4층</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/me/kisgym</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>204</v>
+      </c>
+      <c r="R72" t="n">
+        <v>318</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1061279310</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1061279310</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>스웻먼데이</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>yisl15047@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 뚝섬로 311 서울숲 대림아파트상가 지층 스웻먼데이</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wwzd10a</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>18</v>
+      </c>
+      <c r="R73" t="n">
+        <v>47</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>2053183634</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2053183634</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>폭스짐</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>dana628@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>02-464-4988</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 상원길 59 B동 206호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dana628</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>85</v>
+      </c>
+      <c r="R74" t="n">
+        <v>92</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>35688796</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35688796</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>리메이크짐PT 왕십리점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>remakegym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1316-1768</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 행당로17길 1-57 B1</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45xxc</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>215</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>145</v>
+      </c>
+      <c r="R75" t="n">
+        <v>360</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1813123403</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1813123403</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>프로짐 헬스&amp;P.T</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>pro-gym1557@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 마장로 191 3층</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pro-gym1557</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>9</v>
+      </c>
+      <c r="R76" t="n">
+        <v>45</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>36233969</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36233969</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>원더바레 왕십리점</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>wonderbarre_ws@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1420-3937</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무학봉16길 3 3층</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://wonderbarre-ws.vercel.app/</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>76</v>
+      </c>
+      <c r="R77" t="n">
+        <v>170</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>2036135870</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2036135870</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>프롬더스트릿 with 오버맥스짐</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>fromthestreet@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1339-1637</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 행당로17길 7 지하 1층/2층</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://jfromthestreet.com/</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>1087</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>585</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1672</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1716930812</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1716930812</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>밋 왕십리점</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>letsmiit@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ceo@letsmiit.com</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1361-9430</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 고산자로 211 지하1층</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>http://letsmiit.com</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ttgf</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>43</v>
+      </c>
+      <c r="R79" t="n">
+        <v>159</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1239339806</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1239339806</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>밋 왕십리 센트라스점</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>kuk5837@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1408-3579</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 410 센트라스 상가H동 204, 205호</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/miit_workout/</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>209</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>153</v>
+      </c>
+      <c r="R80" t="n">
+        <v>362</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1350868163</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1350868163</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>더블와이짐 헬스&amp;PT 행당점</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>doubleygym4@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1383-7653</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 행당로 84 4층 더블와이짐</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w0qu5ng</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>711</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>241</v>
+      </c>
+      <c r="R81" t="n">
+        <v>952</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>2052050963</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2052050963</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>피앤디 서울숲2호점</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>pndpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1340-3055</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 둘레1길 14 예나빌딩 B1 피앤디</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w443ry</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>46</v>
+      </c>
+      <c r="R82" t="n">
+        <v>96</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1402669349</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1402669349</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>하이엔드짐 헬스&amp;PT 왕십리점</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>highend_fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1369-3937</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 257 지하 1층</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://highendgymws-landing.vercel.app/</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44o3h</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>577</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1775</v>
+      </c>
+      <c r="R83" t="n">
+        <v>2352</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1010588359</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1010588359</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>위드짐 PT&amp;헬스 금호점</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1stdscho@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1318-9690</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 금호로 40 B1 (20-8, 20-9)</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc6gu9</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>110</v>
+      </c>
+      <c r="R84" t="n">
+        <v>252</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1134766409</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1134766409</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>오늘운동 왕십리점</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>onlundong@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1315-4516</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 무학로 33 152동 B107호</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4i386</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>192</v>
+      </c>
+      <c r="R85" t="n">
+        <v>221</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1028637040</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1028637040</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>리피티 재활PT 왕십리점</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>recompany__@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1476-3782</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 행당로17길 1-57 지하1층</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wm21f2c</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>569</v>
+      </c>
+      <c r="R86" t="n">
+        <v>696</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>2047161310</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2047161310</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>운동의정석 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ckrgksrmsdnj@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>02-3395-9193</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 322 B1층 운동의 정석 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f78l</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>389</v>
+      </c>
+      <c r="R87" t="n">
+        <v>589</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1452177609</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1452177609</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>에이블짐 한양대점</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ablegym13@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1354-9684</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 마조로 30 지하1층 에이블짐 한양대점</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4i2wx</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>1501</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1350</v>
+      </c>
+      <c r="R88" t="n">
+        <v>2851</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1964150912</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1964150912</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>센트리얼 휘트니스&amp;골프&amp;요가 옥수점</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>centrealoksu@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1429-3024</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로40길 39 옥수어울림 상가 B1층</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyfpqqy</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>515</v>
+      </c>
+      <c r="R89" t="n">
+        <v>736</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1693279616</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1693279616</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>뭉트니스 옥수점 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>mtns_oksu@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1365-9722</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로 226 2층</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>338</v>
+      </c>
+      <c r="R90" t="n">
+        <v>701</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>1646071896</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1646071896</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>투엑스휘트니스 옥수 GDR골프아카데미</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2xfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1468-0451</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로 166 한남더리버오피스텔 1F/B1/B2</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>945</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>133</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1078</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>272888535</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/272888535</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>더컨디셔닝</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>theconditioning@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1428-1119</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 금호로 127 금호자이1차</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcahvx</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>23</v>
+      </c>
+      <c r="R92" t="n">
+        <v>31</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>38274742</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38274742</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>가미핏</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>gamifit@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0507-1429-4080</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 독서당로51길 8 지하1층</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>26</v>
+      </c>
+      <c r="R93" t="n">
+        <v>26</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>1064152544</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1064152544</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>체력단련,운동</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>프롬더바디</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>fromthebody@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0507-1376-1296</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 115 헤이그라운드 9층 (주)프롬더바디</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4q1q7</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>16</v>
+      </c>
+      <c r="R94" t="n">
+        <v>28</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>1102389103</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1102389103</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>휴펫필라테스 &amp; PT 상왕십리점</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>hu_pet@naver.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0507-1411-7117</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 410 센트라스 L동 상가 1층 119호</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>http://www.hupetpilates.com/</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4k31g</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>679</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>356</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1035</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>1201969719</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1201969719</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>엘투휘트니스 왕십리점</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>l2fitness02@naver.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0507-1384-3810</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 마장로 137 텐즈힐상가 1층</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yr03</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>1644</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>596</v>
+      </c>
+      <c r="R96" t="n">
+        <v>2240</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>1737638021</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1737638021</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>스포애니 왕십리역점</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>spoany88s@naver.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0507-1493-0215</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 326 세신빌딩 지하1층</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ewpy</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>1229</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1750</v>
+      </c>
+      <c r="R97" t="n">
+        <v>2979</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>1006755563</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1006755563</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>파크짐 한양대점</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>parkgymhyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>02-3395-1522</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>서울특별시 성동구 왕십리로 223 B1,B2층</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wibt8ju</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>612</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1007</v>
+      </c>
+      <c r="R98" t="n">
+        <v>1619</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>1614859791</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1614859791</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
